--- a/branches/testing-only/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/testing-only/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-12T13:14:32+00:00</t>
+    <t>2023-06-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/testing-only/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/testing-only/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-20T13:48:39+00:00</t>
+    <t>2023-06-20T13:48:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
